--- a/input/Domains/Game/RewardTable.xlsx
+++ b/input/Domains/Game/RewardTable.xlsx
@@ -1,46 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93429E6-7FCF-C247-A07E-16A035F69C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="39640" yWindow="-1700" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="REWARD" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+  <si>
+    <t>rewardNum</t>
+  </si>
+  <si>
+    <t>rewardGroupId</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>enum:REWARD_TYPE</t>
+  </si>
+  <si>
+    <t>pk</t>
+  </si>
+  <si>
+    <t>group:true</t>
+  </si>
+  <si>
+    <t>Reward PK (auto-increment number)</t>
+  </si>
+  <si>
+    <t>Reward Group Key</t>
+  </si>
+  <si>
+    <t>Reward Type</t>
+  </si>
+  <si>
+    <t>Target ID</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>reward_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>GOLD</t>
+  </si>
+  <si>
+    <t>JEWEL_PAID</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,13 +121,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,72 +460,111 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>rewardNum</v>
-      </c>
-      <c r="B1" t="str">
-        <v>rewardGroupId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>id</v>
-      </c>
-      <c r="E1" t="str">
-        <v>amount</v>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>int</v>
-      </c>
-      <c r="B2" t="str">
-        <v>string</v>
-      </c>
-      <c r="C2" t="str">
-        <v>enum:REWARD_TYPE</v>
-      </c>
-      <c r="D2" t="str">
-        <v>string</v>
-      </c>
-      <c r="E2" t="str">
-        <v>int</v>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>pk</v>
-      </c>
-      <c r="B3" t="str">
-        <v>group:true</v>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Reward PK (auto-increment number)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Reward Group Key</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Reward Type</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Target ID</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Amount</v>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError sqref="A1:E4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input/Domains/Game/RewardTable.xlsx
+++ b/input/Domains/Game/RewardTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93429E6-7FCF-C247-A07E-16A035F69C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F70DDE-A0C8-AC4C-8DE8-96EACACFA044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39640" yWindow="-1700" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1660" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REWARD" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>rewardNum</t>
   </si>
@@ -67,17 +67,41 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>reward_001</t>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>GOLD</t>
+  </si>
+  <si>
+    <t>JEWEL_PAID</t>
+  </si>
+  <si>
+    <t>RENTAL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CURRENCY</t>
-  </si>
-  <si>
-    <t>GOLD</t>
-  </si>
-  <si>
-    <t>JEWEL_PAID</t>
+    <t>SEASON_PASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO_ADS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S2026_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_pass_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_chest_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_noads_month</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -461,9 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
+    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -531,13 +556,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
       </c>
       <c r="E5">
         <v>1000</v>
@@ -548,16 +573,50 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/input/Domains/Game/RewardTable.xlsx
+++ b/input/Domains/Game/RewardTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F70DDE-A0C8-AC4C-8DE8-96EACACFA044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582F4213-947C-0A45-978A-E441ED58A560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1660" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39800" yWindow="-2320" windowWidth="36980" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REWARD" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>rewardNum</t>
   </si>
@@ -102,6 +102,42 @@
   <si>
     <t>reward_noads_month</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_mission_day_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_mission_day_002</t>
+  </si>
+  <si>
+    <t>reward_mission_day_003</t>
+  </si>
+  <si>
+    <t>reward_mission_day_004</t>
+  </si>
+  <si>
+    <t>reward_mission_day_005</t>
+  </si>
+  <si>
+    <t>reward_mission_achieve_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JEWEL_FREE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_mission_achieve_002</t>
+  </si>
+  <si>
+    <t>reward_mission_achieve_003</t>
+  </si>
+  <si>
+    <t>reward_mission_achieve_004</t>
+  </si>
+  <si>
+    <t>reward_mission_achieve_005</t>
   </si>
 </sst>
 </file>
@@ -485,10 +521,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -617,6 +653,176 @@
       </c>
       <c r="E8">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
